--- a/Convert_from_xlsx_to_Json/table_normalization/environment-table18.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/environment-table18.xlsx
@@ -586,14 +586,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -611,6 +607,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -920,7 +920,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1351,28 +1351,28 @@
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="41" t="s">
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="40" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.149999999999999" customHeight="1">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="48" t="s">
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="46" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="56.25" customHeight="1">
-      <c r="A7" s="43"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="9" t="s">
         <v>8</v>
       </c>
@@ -1382,7 +1382,7 @@
       <c r="D7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="49"/>
+      <c r="E7" s="47"/>
     </row>
     <row r="8" spans="1:5" ht="15.9" customHeight="1">
       <c r="A8" s="10" t="s">
@@ -2128,7 +2128,7 @@
       </c>
     </row>
     <row r="55" spans="1:5" ht="18">
-      <c r="A55" s="46" t="s">
+      <c r="A55" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B55" s="28">
@@ -2145,7 +2145,7 @@
       </c>
     </row>
     <row r="56" spans="1:5" ht="17.5">
-      <c r="A56" s="47" t="s">
+      <c r="A56" s="45" t="s">
         <v>58</v>
       </c>
       <c r="B56" s="29">
